--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>5.83</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>42.22</v>
+        <v>42.23</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>36.4</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
